--- a/data/trans_orig/P1417-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1417-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de anemia en 2007</t>
+          <t>Población con diagnóstico de anemia en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9254</t>
+          <t>10816</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>957</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7806</t>
+          <t>8522</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2036</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12586</t>
+          <t>14765</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>464522</t>
+          <t>462960</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>298874</t>
+          <t>298158</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>305703</t>
+          <t>305723</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>767871</t>
+          <t>765692</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>778436</t>
+          <t>778421</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4604</t>
+          <t>4184</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11689</t>
+          <t>10960</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>2178</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12576</t>
+          <t>12933</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>362330</t>
+          <t>362750</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>360176</t>
+          <t>360905</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>369883</t>
+          <t>369899</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>726223</t>
+          <t>725866</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>736291</t>
+          <t>736621</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>818</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10167</t>
+          <t>9545</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2084</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12053</t>
+          <t>12663</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4536</t>
+          <t>4571</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17710</t>
+          <t>17256</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>532222</t>
+          <t>532844</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>541577</t>
+          <t>541571</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155729</t>
+          <t>155119</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165758</t>
+          <t>165698</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>692461</t>
+          <t>692915</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>705635</t>
+          <t>705600</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>7110</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4056</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15885</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5480</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18242</t>
+          <t>19261</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1232346</t>
+          <t>1231224</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>698400</t>
+          <t>697821</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>710229</t>
+          <t>710354</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1934378</t>
+          <t>1933359</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1947140</t>
+          <t>1947222</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1741</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9931</t>
+          <t>10332</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>6004</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19950</t>
+          <t>21536</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9341</t>
+          <t>8509</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26429</t>
+          <t>24635</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>340624</t>
+          <t>340223</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>348814</t>
+          <t>348835</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>548802</t>
+          <t>547216</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>563269</t>
+          <t>562748</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>892878</t>
+          <t>894672</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>909966</t>
+          <t>910798</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14710</t>
+          <t>15189</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34064</t>
+          <t>34884</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14858</t>
+          <t>14539</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34345</t>
+          <t>34103</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>296337</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>298201</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1214696</t>
+          <t>1213876</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1234050</t>
+          <t>1233571</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1512615</t>
+          <t>1512857</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1532102</t>
+          <t>1532421</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7219</t>
+          <t>7319</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23546</t>
+          <t>22521</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44889</t>
+          <t>43663</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>75463</t>
+          <t>74685</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>55520</t>
+          <t>56261</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>90221</t>
+          <t>90494</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3246644</t>
+          <t>3247669</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3262971</t>
+          <t>3262871</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3302661</t>
+          <t>3303439</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3333235</t>
+          <t>3334461</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6558093</t>
+          <t>6557820</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6592794</t>
+          <t>6592053</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de anemia en 2012</t>
+          <t>Población con diagnóstico de anemia en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7014</t>
+          <t>6275</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14302</t>
+          <t>14393</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4151</t>
+          <t>4821</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16527</t>
+          <t>16364</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>430197</t>
+          <t>430936</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>300152</t>
+          <t>300061</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311426</t>
+          <t>311414</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>735138</t>
+          <t>735301</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>747514</t>
+          <t>746844</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4273</t>
+          <t>6235</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3094</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14514</t>
+          <t>15684</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4046</t>
+          <t>3939</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15699</t>
+          <t>15841</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>414524</t>
+          <t>412562</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>323497</t>
+          <t>322327</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>334917</t>
+          <t>334810</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>741109</t>
+          <t>740967</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>752762</t>
+          <t>752869</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>5256</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1853</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11791</t>
+          <t>11037</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12793</t>
+          <t>12481</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>624536</t>
+          <t>624159</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>248338</t>
+          <t>249092</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>258276</t>
+          <t>258224</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>876751</t>
+          <t>877063</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>887478</t>
+          <t>887502</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3112</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14478</t>
+          <t>14880</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4417,77 +4417,77 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>16789</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>10332</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>26986</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>3,53%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>23993</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>15586</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>35224</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
           <t>1,25%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>16789</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>9588</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>27366</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>3,58%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>23993</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>15745</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>36084</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1144531</t>
+          <t>1144129</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1155928</t>
+          <t>1155897</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,82 +4525,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>98,72%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>747933</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>737736</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>754390</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>97,8%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>96,47%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>98,65%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1770</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1899738</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1888507</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1908145</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>98,75%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>694</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>747933</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>737356</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>755134</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,8%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>96,42%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>98,75%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1770</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1899738</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1887647</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1907986</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>98,75%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10856</t>
+          <t>10005</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21756</t>
+          <t>22481</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45679</t>
+          <t>47838</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25390</t>
+          <t>24457</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51573</t>
+          <t>51340</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>499740</t>
+          <t>500591</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>509604</t>
+          <t>509595</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>714567</t>
+          <t>712408</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>738490</t>
+          <t>737765</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1219270</t>
+          <t>1219503</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1245453</t>
+          <t>1246386</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17815</t>
+          <t>17238</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>38711</t>
+          <t>38305</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17610</t>
+          <t>17345</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38275</t>
+          <t>38671</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264956</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266882</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1069594</t>
+          <t>1070000</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1090490</t>
+          <t>1091067</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1336912</t>
+          <t>1336516</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1357577</t>
+          <t>1357842</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8388</t>
+          <t>9037</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24805</t>
+          <t>24533</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>76465</t>
+          <t>78163</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>115484</t>
+          <t>118567</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>90585</t>
+          <t>91497</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>132826</t>
+          <t>134784</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3397105</t>
+          <t>3397377</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3413522</t>
+          <t>3412873</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3430384</t>
+          <t>3427301</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3469403</t>
+          <t>3467705</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6834952</t>
+          <t>6832994</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6877193</t>
+          <t>6876281</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de anemia en 2016</t>
+          <t>Población con diagnóstico de anemia en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6651</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10280</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>903</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11963</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>422441</t>
+          <t>423195</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>336775</t>
+          <t>337274</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>764184</t>
+          <t>764959</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>775238</t>
+          <t>775244</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>902</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8445</t>
+          <t>8206</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11790</t>
+          <t>10902</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>3913</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>15118</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>368782</t>
+          <t>369021</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>376309</t>
+          <t>376325</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>360483</t>
+          <t>361371</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>734473</t>
+          <t>734382</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>745543</t>
+          <t>745587</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1596</t>
+          <t>1816</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11323</t>
+          <t>11296</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3258</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14094</t>
+          <t>13748</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6420</t>
+          <t>6874</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20210</t>
+          <t>21624</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>510591</t>
+          <t>510618</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>520318</t>
+          <t>520098</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>152029</t>
+          <t>152375</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162865</t>
+          <t>163017</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>667826</t>
+          <t>666412</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>681616</t>
+          <t>681162</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11044</t>
+          <t>10991</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11163</t>
+          <t>11180</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29352</t>
+          <t>28960</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15450</t>
+          <t>15688</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35222</t>
+          <t>34632</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1138594</t>
+          <t>1138647</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1147854</t>
+          <t>1147716</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>796524</t>
+          <t>796916</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>814713</t>
+          <t>814696</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1940292</t>
+          <t>1940882</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1960064</t>
+          <t>1959826</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>894</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7842</t>
+          <t>8671</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21592</t>
+          <t>21494</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44411</t>
+          <t>43147</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23586</t>
+          <t>24378</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46492</t>
+          <t>48111</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>612864</t>
+          <t>612035</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>619826</t>
+          <t>619812</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>693833</t>
+          <t>695097</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>716652</t>
+          <t>716750</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1312458</t>
+          <t>1310839</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1335364</t>
+          <t>1334572</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7116</t>
+          <t>6294</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12967</t>
+          <t>12481</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32054</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14154</t>
+          <t>15124</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34079</t>
+          <t>34053</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>280029</t>
+          <t>280851</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1049971</t>
+          <t>1050359</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1069058</t>
+          <t>1069544</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1335091</t>
+          <t>1335117</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1355016</t>
+          <t>1354046</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11451</t>
+          <t>11754</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29942</t>
+          <t>29059</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>67763</t>
+          <t>69071</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>106083</t>
+          <t>105327</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>85258</t>
+          <t>85568</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>128253</t>
+          <t>127291</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3355780</t>
+          <t>3356663</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3374271</t>
+          <t>3373968</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3425513</t>
+          <t>3426269</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3463833</t>
+          <t>3462525</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6789065</t>
+          <t>6790027</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6832060</t>
+          <t>6831750</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de anemia en 2023</t>
+          <t>Población con diagnóstico de anemia en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>339</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4885</t>
+          <t>5428</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11213</t>
+          <t>11131</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25005</t>
+          <t>24820</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12684</t>
+          <t>12800</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27526</t>
+          <t>27183</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>500327</t>
+          <t>499784</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>504686</t>
+          <t>504873</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>422462</t>
+          <t>422647</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>436254</t>
+          <t>436336</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>925153</t>
+          <t>925496</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>939995</t>
+          <t>939879</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8306</t>
+          <t>9089</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7946</t>
+          <t>8117</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20267</t>
+          <t>19562</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10261</t>
+          <t>10373</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23346</t>
+          <t>23359</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>443907</t>
+          <t>443124</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>451172</t>
+          <t>451143</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>361644</t>
+          <t>362349</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>373965</t>
+          <t>373794</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>810778</t>
+          <t>810765</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>823863</t>
+          <t>823751</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1456</t>
+          <t>1374</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14625</t>
+          <t>15070</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12575</t>
+          <t>12969</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>5525</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24356</t>
+          <t>25117</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>651607</t>
+          <t>651162</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>664776</t>
+          <t>664858</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>154034</t>
+          <t>153640</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162416</t>
+          <t>162275</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>808485</t>
+          <t>807724</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>827694</t>
+          <t>827316</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8864</t>
+          <t>8554</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21689</t>
+          <t>21507</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11936</t>
+          <t>10869</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34285</t>
+          <t>33556</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25746</t>
+          <t>25714</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50118</t>
+          <t>49405</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9757,7 +9757,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1013130</t>
+          <t>1013312</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1025955</t>
+          <t>1026265</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>941982</t>
+          <t>942711</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>964331</t>
+          <t>965398</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1960967</t>
+          <t>1961680</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1985339</t>
+          <t>1985371</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6994</t>
+          <t>6617</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17677</t>
+          <t>17565</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34510</t>
+          <t>36241</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61761</t>
+          <t>62523</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45911</t>
+          <t>46913</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>73816</t>
+          <t>73703</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>454393</t>
+          <t>454505</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>465076</t>
+          <t>465453</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>776021</t>
+          <t>775259</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>803272</t>
+          <t>801541</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1236035</t>
+          <t>1236148</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1263940</t>
+          <t>1262938</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,42%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4080</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28703</t>
+          <t>28370</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55991</t>
+          <t>54871</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27374</t>
+          <t>27788</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>54266</t>
+          <t>54139</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>236427</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>704151</t>
+          <t>705271</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>731439</t>
+          <t>731772</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>946383</t>
+          <t>946510</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>973275</t>
+          <t>972861</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27093</t>
+          <t>26493</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49258</t>
+          <t>48551</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>120888</t>
+          <t>119619</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>173601</t>
+          <t>173339</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>157068</t>
+          <t>155946</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>216422</t>
+          <t>212619</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3321794</t>
+          <t>3322501</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3343959</t>
+          <t>3344559</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3396576</t>
+          <t>3396838</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3449289</t>
+          <t>3450558</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6724808</t>
+          <t>6728611</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6784162</t>
+          <t>6785284</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1417-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1417-Clase-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10816</t>
+          <t>9617</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>975</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8522</t>
+          <t>7737</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14765</t>
+          <t>14866</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>462960</t>
+          <t>464159</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>298158</t>
+          <t>298943</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>305723</t>
+          <t>305705</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>765692</t>
+          <t>765591</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>778421</t>
+          <t>778468</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4184</t>
+          <t>5448</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>2093</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10960</t>
+          <t>11848</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2178</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12933</t>
+          <t>13081</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>362750</t>
+          <t>361486</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>360905</t>
+          <t>360017</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>369899</t>
+          <t>369772</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>725866</t>
+          <t>725718</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>736621</t>
+          <t>736685</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>814</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9545</t>
+          <t>10057</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>2087</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12663</t>
+          <t>12939</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4571</t>
+          <t>4164</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17256</t>
+          <t>17118</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>532844</t>
+          <t>532332</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>541571</t>
+          <t>541575</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155119</t>
+          <t>154843</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165698</t>
+          <t>165695</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>692915</t>
+          <t>693053</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>705600</t>
+          <t>706007</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7110</t>
+          <t>6767</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>4173</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>15822</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,39 +1812,39 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>10744</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>5427</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>18575</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
           <t>0,55%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>10744</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>5398</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>19261</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,28%</t>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1231224</t>
+          <t>1231567</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>697821</t>
+          <t>698463</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>710354</t>
+          <t>710112</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,42 +1925,42 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>99,42%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1907</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1941876</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1934045</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1947193</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>99,45%</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1907</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1941876</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1933359</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1947222</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1720</t>
+          <t>1775</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10332</t>
+          <t>11187</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6004</t>
+          <t>5707</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21536</t>
+          <t>20059</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8509</t>
+          <t>9562</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24635</t>
+          <t>26267</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>340223</t>
+          <t>339368</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>348835</t>
+          <t>348780</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>547216</t>
+          <t>548693</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>562748</t>
+          <t>563045</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>894672</t>
+          <t>893040</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>910798</t>
+          <t>909745</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15189</t>
+          <t>14925</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34884</t>
+          <t>35033</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14539</t>
+          <t>14372</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34103</t>
+          <t>34611</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1213876</t>
+          <t>1213727</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1233571</t>
+          <t>1233835</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1512857</t>
+          <t>1512349</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1532421</t>
+          <t>1532588</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7319</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22521</t>
+          <t>22185</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43663</t>
+          <t>44752</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>74685</t>
+          <t>73864</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>56261</t>
+          <t>56389</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>90494</t>
+          <t>90892</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3247669</t>
+          <t>3248005</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3262871</t>
+          <t>3262998</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3303439</t>
+          <t>3304260</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3334461</t>
+          <t>3333372</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6557820</t>
+          <t>6557422</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6592053</t>
+          <t>6591925</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6275</t>
+          <t>7133</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14393</t>
+          <t>14174</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4821</t>
+          <t>4818</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16364</t>
+          <t>17782</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>430936</t>
+          <t>430078</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>300061</t>
+          <t>300280</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311414</t>
+          <t>311405</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>735301</t>
+          <t>733883</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>746844</t>
+          <t>746847</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6235</t>
+          <t>5113</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15684</t>
+          <t>14475</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>3155</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15841</t>
+          <t>16786</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>412562</t>
+          <t>413684</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>322327</t>
+          <t>323536</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>334810</t>
+          <t>334885</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>740967</t>
+          <t>740022</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>752869</t>
+          <t>753653</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5256</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1878</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11037</t>
+          <t>10983</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12481</t>
+          <t>12315</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>624159</t>
+          <t>624131</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>249092</t>
+          <t>249146</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>258224</t>
+          <t>258251</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>877063</t>
+          <t>877229</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>887502</t>
+          <t>887565</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3112</t>
+          <t>3067</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14880</t>
+          <t>13966</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10332</t>
+          <t>10428</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26986</t>
+          <t>27278</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15586</t>
+          <t>15748</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35224</t>
+          <t>35490</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1144129</t>
+          <t>1145043</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1155897</t>
+          <t>1155942</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>737736</t>
+          <t>737444</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>754390</t>
+          <t>754294</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1888507</t>
+          <t>1888241</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1908145</t>
+          <t>1907983</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>982</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10005</t>
+          <t>9688</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22481</t>
+          <t>21564</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47838</t>
+          <t>47785</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24457</t>
+          <t>25970</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51340</t>
+          <t>51701</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>500591</t>
+          <t>500908</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>509595</t>
+          <t>509614</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>712408</t>
+          <t>712461</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>737765</t>
+          <t>738682</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1219503</t>
+          <t>1219142</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1246386</t>
+          <t>1244873</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17238</t>
+          <t>17326</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>38305</t>
+          <t>38699</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17345</t>
+          <t>17378</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38671</t>
+          <t>38659</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1070000</t>
+          <t>1069606</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1091067</t>
+          <t>1090979</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1336516</t>
+          <t>1336528</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1357842</t>
+          <t>1357809</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9037</t>
+          <t>9086</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24533</t>
+          <t>24518</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>78163</t>
+          <t>78838</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>118567</t>
+          <t>117618</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>91497</t>
+          <t>90484</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>134784</t>
+          <t>134727</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3397377</t>
+          <t>3397392</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3412873</t>
+          <t>3412824</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3427301</t>
+          <t>3428250</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3467705</t>
+          <t>3467030</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6832994</t>
+          <t>6833051</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6876281</t>
+          <t>6877294</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>5653</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9781</t>
+          <t>11709</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>906</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11188</t>
+          <t>12280</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>423195</t>
+          <t>423439</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>337274</t>
+          <t>335346</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>764959</t>
+          <t>763867</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>775244</t>
+          <t>775241</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>907</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>9011</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1894</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3913</t>
+          <t>3751</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15118</t>
+          <t>14824</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>369021</t>
+          <t>368216</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>376325</t>
+          <t>376320</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6499,7 +6499,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>370373</t>
+          <t>370379</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>734382</t>
+          <t>734676</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>745587</t>
+          <t>745749</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>1930</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11296</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13748</t>
+          <t>13365</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6874</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21624</t>
+          <t>21456</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>510618</t>
+          <t>510048</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>520098</t>
+          <t>519984</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>152375</t>
+          <t>152758</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>163017</t>
+          <t>163008</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>666412</t>
+          <t>666580</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>681162</t>
+          <t>681840</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10991</t>
+          <t>11028</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11180</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28960</t>
+          <t>29417</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15688</t>
+          <t>15849</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34632</t>
+          <t>35010</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1138647</t>
+          <t>1138610</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1147716</t>
+          <t>1147715</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>796916</t>
+          <t>796459</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>814696</t>
+          <t>813972</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1940882</t>
+          <t>1940504</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1959826</t>
+          <t>1959665</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>895</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8671</t>
+          <t>8875</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21494</t>
+          <t>21104</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43147</t>
+          <t>43204</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24378</t>
+          <t>23725</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48111</t>
+          <t>47127</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>612035</t>
+          <t>611831</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>619812</t>
+          <t>619811</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>695097</t>
+          <t>695040</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>716750</t>
+          <t>717140</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1310839</t>
+          <t>1311823</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1334572</t>
+          <t>1335225</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6294</t>
+          <t>7097</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12481</t>
+          <t>12820</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>32527</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15124</t>
+          <t>13399</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34053</t>
+          <t>34302</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>280851</t>
+          <t>280048</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1050359</t>
+          <t>1049498</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1069544</t>
+          <t>1069205</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1335117</t>
+          <t>1334868</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1354046</t>
+          <t>1355771</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11754</t>
+          <t>11543</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29059</t>
+          <t>28679</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>69071</t>
+          <t>69298</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>105327</t>
+          <t>106722</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>85568</t>
+          <t>85742</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>127291</t>
+          <t>127297</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3356663</t>
+          <t>3357043</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3373968</t>
+          <t>3374179</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3426269</t>
+          <t>3424874</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3462525</t>
+          <t>3462298</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,7 +8224,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6790027</t>
+          <t>6790021</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6831750</t>
+          <t>6831576</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1819</t>
+          <t>2861</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>864</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5428</t>
+          <t>7589</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>16925</t>
+          <t>17136</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11131</t>
+          <t>11337</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24820</t>
+          <t>25752</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>18745</t>
+          <t>19997</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12800</t>
+          <t>13530</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27183</t>
+          <t>28662</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>503393</t>
+          <t>547757</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>499784</t>
+          <t>543029</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>504873</t>
+          <t>549754</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>430542</t>
+          <t>471275</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>422647</t>
+          <t>462659</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>436336</t>
+          <t>477074</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>933934</t>
+          <t>1019032</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>925496</t>
+          <t>1010367</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>939879</t>
+          <t>1025499</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3199</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1192</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9089</t>
+          <t>8915</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12825</t>
+          <t>14035</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8117</t>
+          <t>9457</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19562</t>
+          <t>21330</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>16024</t>
+          <t>17959</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10373</t>
+          <t>11813</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23359</t>
+          <t>26804</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>449014</t>
+          <t>479288</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>443124</t>
+          <t>474297</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>451143</t>
+          <t>482020</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>369086</t>
+          <t>408457</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>362349</t>
+          <t>401162</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>373794</t>
+          <t>413035</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>818100</t>
+          <t>887745</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>810765</t>
+          <t>878900</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>823751</t>
+          <t>893891</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>381911</t>
+          <t>422492</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>381911</t>
+          <t>422492</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>381911</t>
+          <t>422492</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834124</t>
+          <t>905704</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834124</t>
+          <t>905704</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834124</t>
+          <t>905704</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7002</t>
+          <t>6964</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1374</t>
+          <t>3239</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15070</t>
+          <t>13350</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7648</t>
+          <t>8507</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12969</t>
+          <t>14285</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>14650</t>
+          <t>15471</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5525</t>
+          <t>9446</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25117</t>
+          <t>23007</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>659230</t>
+          <t>462446</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>651162</t>
+          <t>456060</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>664858</t>
+          <t>466171</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>158961</t>
+          <t>178708</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>153640</t>
+          <t>172930</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162275</t>
+          <t>182330</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>818191</t>
+          <t>641153</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>807724</t>
+          <t>633617</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>827316</t>
+          <t>647178</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>666232</t>
+          <t>469410</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>666232</t>
+          <t>469410</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>666232</t>
+          <t>469410</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166609</t>
+          <t>187215</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166609</t>
+          <t>187215</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166609</t>
+          <t>187215</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>832841</t>
+          <t>656624</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>832841</t>
+          <t>656624</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>832841</t>
+          <t>656624</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13991</t>
+          <t>15492</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8554</t>
+          <t>10252</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21507</t>
+          <t>23619</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23775</t>
+          <t>27023</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10869</t>
+          <t>19883</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33556</t>
+          <t>36260</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>37766</t>
+          <t>42515</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25714</t>
+          <t>32861</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49405</t>
+          <t>53440</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1020828</t>
+          <t>1116351</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1013312</t>
+          <t>1108224</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1026265</t>
+          <t>1121591</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>952492</t>
+          <t>832275</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>942711</t>
+          <t>823038</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>965398</t>
+          <t>839415</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1973319</t>
+          <t>1948626</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1961680</t>
+          <t>1937701</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1985371</t>
+          <t>1958280</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>976267</t>
+          <t>859298</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>976267</t>
+          <t>859298</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>976267</t>
+          <t>859298</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2011085</t>
+          <t>1991141</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2011085</t>
+          <t>1991141</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2011085</t>
+          <t>1991141</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11250</t>
+          <t>12795</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6617</t>
+          <t>8002</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17565</t>
+          <t>20916</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>48496</t>
+          <t>55884</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36241</t>
+          <t>43407</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62523</t>
+          <t>67904</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>59745</t>
+          <t>68679</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>46913</t>
+          <t>55779</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>73703</t>
+          <t>83044</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>460820</t>
+          <t>551805</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>454505</t>
+          <t>543684</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>465453</t>
+          <t>556598</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>789286</t>
+          <t>772845</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>775259</t>
+          <t>760825</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>801541</t>
+          <t>785322</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1250106</t>
+          <t>1324651</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1236148</t>
+          <t>1310286</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1262938</t>
+          <t>1337551</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,0%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>472070</t>
+          <t>564600</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>472070</t>
+          <t>564600</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>472070</t>
+          <t>564600</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>837782</t>
+          <t>828729</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>837782</t>
+          <t>828729</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>837782</t>
+          <t>828729</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1309851</t>
+          <t>1393330</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1309851</t>
+          <t>1393330</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1309851</t>
+          <t>1393330</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>38182</t>
+          <t>38414</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28370</t>
+          <t>28402</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>54871</t>
+          <t>51637</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>38181</t>
+          <t>38414</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27788</t>
+          <t>28854</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>54139</t>
+          <t>51043</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -10461,7 +10461,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>721960</t>
+          <t>804567</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>705271</t>
+          <t>791344</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>731772</t>
+          <t>814579</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>962468</t>
+          <t>1041794</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>946510</t>
+          <t>1029165</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>972861</t>
+          <t>1051354</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760142</t>
+          <t>842981</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760142</t>
+          <t>842981</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760142</t>
+          <t>842981</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000649</t>
+          <t>1080208</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000649</t>
+          <t>1080208</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000649</t>
+          <t>1080208</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>37260</t>
+          <t>42035</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26493</t>
+          <t>32125</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48551</t>
+          <t>55050</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>147850</t>
+          <t>160999</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>119619</t>
+          <t>142275</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>173339</t>
+          <t>183489</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>185111</t>
+          <t>203033</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>155946</t>
+          <t>180988</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>212619</t>
+          <t>227319</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3333792</t>
+          <t>3394876</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3322501</t>
+          <t>3381861</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3344559</t>
+          <t>3404786</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3422327</t>
+          <t>3468126</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3396838</t>
+          <t>3445636</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3450558</t>
+          <t>3486850</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6756119</t>
+          <t>6863003</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6728611</t>
+          <t>6838717</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6785284</t>
+          <t>6885048</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,44%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3371052</t>
+          <t>3436911</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3371052</t>
+          <t>3436911</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3371052</t>
+          <t>3436911</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3570177</t>
+          <t>3629125</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3570177</t>
+          <t>3629125</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3570177</t>
+          <t>3629125</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6941230</t>
+          <t>7066036</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6941230</t>
+          <t>7066036</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6941230</t>
+          <t>7066036</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
